--- a/extended_bridging/tests/fixture_schema.xlsx
+++ b/extended_bridging/tests/fixture_schema.xlsx
@@ -685,8 +685,10 @@
       <c r="AI2" t="n">
         <v>0</v>
       </c>
-      <c r="AJ2" t="n">
-        <v>1</v>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
